--- a/output/roomself_excel/5519.xlsx
+++ b/output/roomself_excel/5519.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46585</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="n">
-        <v>2024</v>
+        <v>2496</v>
       </c>
       <c r="E2" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>310274</v>
+        <v>120505</v>
       </c>
       <c r="D3" t="n">
-        <v>6592</v>
+        <v>2792</v>
       </c>
       <c r="E3" t="n">
-        <v>785</v>
+        <v>415</v>
       </c>
       <c r="F3" t="n">
-        <v>599</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23961</v>
+        <v>82208</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>2364</v>
       </c>
       <c r="E5" t="n">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>2116</v>
       </c>
       <c r="E6" t="n">
-        <v>547</v>
+        <v>361</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82208</v>
+        <v>41548</v>
       </c>
       <c r="D7" t="n">
-        <v>2364</v>
+        <v>1636</v>
       </c>
       <c r="E7" t="n">
-        <v>396</v>
+        <v>246</v>
       </c>
       <c r="F7" t="n">
-        <v>251</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23058</v>
+        <v>97754</v>
       </c>
       <c r="D9" t="n">
-        <v>1244</v>
+        <v>4987</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>599</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41548</v>
+        <v>9944</v>
       </c>
       <c r="D10" t="n">
-        <v>1636</v>
+        <v>804</v>
       </c>
       <c r="E10" t="n">
-        <v>246</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>216</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9944</v>
+        <v>23058</v>
       </c>
       <c r="D11" t="n">
-        <v>804</v>
+        <v>1244</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>46585</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E12" t="n">
+        <v>411</v>
+      </c>
+      <c r="F12" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23961</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E13" t="n">
+        <v>183</v>
+      </c>
+      <c r="F13" t="n">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5519.xlsx
+++ b/output/roomself_excel/5519.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2496</v>
       </c>
-      <c r="E2" t="n">
-        <v>415</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>264</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>385</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>2792</v>
       </c>
-      <c r="E3" t="n">
-        <v>415</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>335</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>385</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>2808</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>341</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>26</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,31 @@
       <c r="D5" t="n">
         <v>2364</v>
       </c>
-      <c r="E5" t="n">
-        <v>396</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>251</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>224</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>2116</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>361</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,31 @@
       <c r="D7" t="n">
         <v>1636</v>
       </c>
-      <c r="E7" t="n">
-        <v>246</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>216</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>221</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,31 @@
       <c r="D8" t="n">
         <v>3424</v>
       </c>
-      <c r="E8" t="n">
-        <v>328</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>217</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>302</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +781,38 @@
       <c r="D9" t="n">
         <v>4987</v>
       </c>
-      <c r="E9" t="n">
-        <v>599</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>370</v>
+        <v>143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>191</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>195</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +830,23 @@
       <c r="D10" t="n">
         <v>804</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>113</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>28</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +863,23 @@
       <c r="D11" t="n">
         <v>1244</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>122</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>22</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +896,38 @@
       <c r="D12" t="n">
         <v>2024</v>
       </c>
-      <c r="E12" t="n">
-        <v>411</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>134</v>
+        <v>385</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>121</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>121</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +945,31 @@
       <c r="D13" t="n">
         <v>1240</v>
       </c>
-      <c r="E13" t="n">
-        <v>183</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>173</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>147</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
